--- a/gte/nodes/P/compressor_blade_parameters.xlsx
+++ b/gte/nodes/P/compressor_blade_parameters.xlsx
@@ -806,121 +806,121 @@
         <v>48</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>121.04351107462517</v>
+        <v>120.63537232201492</v>
       </c>
       <c r="E3">
-        <v>119.68445396205634</v>
+        <v>119.68883096571751</v>
       </c>
       <c r="F3">
-        <v>166.679824597519</v>
+        <v>160.44005436607546</v>
       </c>
       <c r="G3">
-        <v>146.21995755147026</v>
+        <v>143.69121452027341</v>
       </c>
       <c r="H3">
-        <v>397.83760837372506</v>
+        <v>298.37820628029385</v>
       </c>
       <c r="I3">
         <v>2310.3654248608714</v>
       </c>
       <c r="J3">
-        <v>2202.657654152209</v>
+        <v>1529.6572712408008</v>
       </c>
       <c r="K3">
-        <v>48635.316390569344</v>
+        <v>38335.303291132041</v>
       </c>
       <c r="L3">
-        <v>23701.004713116123</v>
+        <v>17775.753534837091</v>
       </c>
       <c r="M3">
-        <v>146612.39974726515</v>
+        <v>146612.39974726512</v>
       </c>
       <c r="N3">
-        <v>59.574570664650714</v>
+        <v>59.5745706646507</v>
       </c>
       <c r="O3">
-        <v>63.458532650130032</v>
+        <v>63.458532650130017</v>
       </c>
       <c r="P3">
-        <v>5.5365747425342757</v>
+        <v>5.1265717101464654</v>
       </c>
       <c r="Q3">
-        <v>21.05091942046273</v>
+        <v>16.59274454102453</v>
       </c>
       <c r="R3">
-        <v>13765.184174677093</v>
+        <v>8737.2908142301822</v>
       </c>
       <c r="S3">
-        <v>1184467.273822539</v>
+        <v>765513.8041404722</v>
       </c>
       <c r="T3">
-        <v>1719636.3744618385</v>
+        <v>1289727.280846379</v>
       </c>
       <c r="U3">
-        <v>11903414.499537855</v>
+        <v>11903414.499537852</v>
       </c>
       <c r="V3">
-        <v>131222.00756686216</v>
+        <v>91128.413733782829</v>
       </c>
       <c r="W3">
-        <v>3202278.6471288814</v>
+        <v>2526203.6457164725</v>
       </c>
       <c r="X3">
-        <v>1570.005440248173</v>
+        <v>895.39312126725383</v>
       </c>
       <c r="Y3">
-        <v>160649.14749595375</v>
+        <v>129425.90972802116</v>
       </c>
       <c r="Z3">
-        <v>307659.19435708213</v>
+        <v>230744.39576781224</v>
       </c>
       <c r="AA3">
         <v>2599606.7432621135</v>
       </c>
       <c r="AB3">
-        <v>-0.37650046241031476</v>
+        <v>-0.26146444902974481</v>
       </c>
       <c r="AC3">
-        <v>115952.83400853281</v>
+        <v>93501.550163532884</v>
       </c>
       <c r="AD3">
-        <v>-7.04758229362116E-05</v>
+        <v>-6.5176743207926856E-05</v>
       </c>
       <c r="AE3">
-        <v>2.7157890804616636</v>
+        <v>2.1646370289668289</v>
       </c>
       <c r="AF3">
-        <v>1570.0054397850643</v>
+        <v>895.39312096982508</v>
       </c>
       <c r="AG3">
-        <v>155148.9258848335</v>
+        <v>125891.73547776503</v>
       </c>
       <c r="AH3">
-        <v>307659.19435754517</v>
+        <v>230744.39576810965</v>
       </c>
       <c r="AI3">
-        <v>2605106.9648732338</v>
+        <v>2603140.91751237</v>
       </c>
       <c r="AJ3">
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.0565374174203953E-11</v>
       </c>
       <c r="AL3">
-        <v>309229.19979733031</v>
+        <v>231639.78888907947</v>
       </c>
       <c r="AM3">
-        <v>2760255.8907580674</v>
+        <v>2729032.6529901344</v>
       </c>
       <c r="AN3">
-        <v>5168.3526388115406</v>
+        <v>3873.9156647877394</v>
       </c>
       <c r="AO3">
-        <v>34556.856214674088</v>
+        <v>34624.369879950536</v>
       </c>
       <c r="AP3">
         <v>41.702079814195237</v>
@@ -1407,121 +1407,121 @@
         <v>48</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>135.60110851030041</v>
+        <v>135.98516468362402</v>
       </c>
       <c r="E3">
-        <v>133.58147678931925</v>
+        <v>133.79405844065406</v>
       </c>
       <c r="F3">
-        <v>169.63344918467703</v>
+        <v>168.63685154782172</v>
       </c>
       <c r="G3">
-        <v>166.3288323500035</v>
+        <v>165.93051067624288</v>
       </c>
       <c r="H3">
-        <v>779.70501885512442</v>
+        <v>649.75418237927056</v>
       </c>
       <c r="I3">
-        <v>1151.8711609832421</v>
+        <v>1202.4881253112892</v>
       </c>
       <c r="J3">
-        <v>3555.2084507985542</v>
+        <v>3844.335145632941</v>
       </c>
       <c r="K3">
-        <v>10418.235426642359</v>
+        <v>7347.8082721965056</v>
       </c>
       <c r="L3">
-        <v>46938.536882303772</v>
+        <v>39115.447401919817</v>
       </c>
       <c r="M3">
-        <v>95338.481765029224</v>
+        <v>89899.0801568266</v>
       </c>
       <c r="N3">
-        <v>60.200378024019528</v>
+        <v>60.200378024019521</v>
       </c>
       <c r="O3">
-        <v>82.768355519594635</v>
+        <v>74.7608880824119</v>
       </c>
       <c r="P3">
-        <v>4.5596839379318412</v>
+        <v>5.9165993076885632</v>
       </c>
       <c r="Q3">
-        <v>9.0446186861291924</v>
+        <v>6.110503810833368</v>
       </c>
       <c r="R3">
-        <v>20850.406732050742</v>
+        <v>26744.921475519492</v>
       </c>
       <c r="S3">
-        <v>108850.60667906463</v>
+        <v>56558.240696904075</v>
       </c>
       <c r="T3">
-        <v>3615129.4194723777</v>
+        <v>3012607.8495603153</v>
       </c>
       <c r="U3">
-        <v>9610400.8666512314</v>
+        <v>8598541.3216663022</v>
       </c>
       <c r="V3">
-        <v>222538.92224954258</v>
+        <v>240616.94014632044</v>
       </c>
       <c r="W3">
-        <v>862297.73958580976</v>
+        <v>571169.88588045351</v>
       </c>
       <c r="X3">
-        <v>4639.7798629450244</v>
+        <v>3999.530814344826</v>
       </c>
       <c r="Y3">
-        <v>14621.639862762013</v>
+        <v>11659.430248374389</v>
       </c>
       <c r="Z3">
-        <v>789411.755263308</v>
+        <v>657843.12938609021</v>
       </c>
       <c r="AA3">
-        <v>1719391.5132249019</v>
+        <v>1877606.2513500128</v>
       </c>
       <c r="AB3">
-        <v>8514.0295572807845</v>
+        <v>9186.5111281932968</v>
       </c>
       <c r="AC3">
-        <v>-2.4740933608513429</v>
+        <v>21841.213991750181</v>
       </c>
       <c r="AD3">
-        <v>0.62150719072452421</v>
+        <v>0.80479467253693349</v>
       </c>
       <c r="AE3">
-        <v>-8.3152048797150815E-05</v>
+        <v>0.6705340330422197</v>
       </c>
       <c r="AF3">
-        <v>4547.4216091755334</v>
+        <v>3870.4856814622713</v>
       </c>
       <c r="AG3">
-        <v>14621.639859171415</v>
+        <v>11403.810269462987</v>
       </c>
       <c r="AH3">
-        <v>789504.11351707752</v>
+        <v>657972.17451897252</v>
       </c>
       <c r="AI3">
-        <v>1719391.5132284924</v>
+        <v>1877861.8713289243</v>
       </c>
       <c r="AJ3">
         <v>-1.0696252980538481E-12</v>
       </c>
       <c r="AK3">
-        <v>3.1055795314704421E-16</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>794051.535126253</v>
+        <v>661842.660200435</v>
       </c>
       <c r="AM3">
-        <v>1734013.1530876642</v>
+        <v>1889265.6815983872</v>
       </c>
       <c r="AN3">
-        <v>10842.08170580196</v>
+        <v>9024.93345452698</v>
       </c>
       <c r="AO3">
-        <v>20826.217462190831</v>
+        <v>20765.54753807111</v>
       </c>
       <c r="AP3">
         <v>46.65367795387116</v>
@@ -2008,34 +2008,34 @@
         <v>48</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>144.67234034991165</v>
+        <v>146.97627631764905</v>
       </c>
       <c r="E3">
-        <v>143.69944760462977</v>
+        <v>143.52817262742016</v>
       </c>
       <c r="F3">
-        <v>182.89044526347939</v>
+        <v>182.76770576831837</v>
       </c>
       <c r="G3">
-        <v>182.68073956846115</v>
+        <v>182.74447621773297</v>
       </c>
       <c r="H3">
-        <v>1196.1212731936685</v>
+        <v>1046.60611404446</v>
       </c>
       <c r="I3">
         <v>701.28049855759764</v>
       </c>
       <c r="J3">
-        <v>1990.7261790697235</v>
+        <v>7084.3324428894921</v>
       </c>
       <c r="K3">
-        <v>785.625082237117</v>
+        <v>87.001188874258219</v>
       </c>
       <c r="L3">
-        <v>77237.375270088509</v>
+        <v>67582.703361327454</v>
       </c>
       <c r="M3">
         <v>64049.3925005803</v>
@@ -2047,82 +2047,82 @@
         <v>91.332059899452346</v>
       </c>
       <c r="P3">
-        <v>1.6643180116297434</v>
+        <v>6.7688620846223593</v>
       </c>
       <c r="Q3">
-        <v>1.1202722503377756</v>
+        <v>0.12406047088604823</v>
       </c>
       <c r="R3">
-        <v>13160.817730471959</v>
+        <v>59051.944931297192</v>
       </c>
       <c r="S3">
-        <v>2172.1587396165687</v>
+        <v>1227.1963803746216</v>
       </c>
       <c r="T3">
-        <v>6381027.673950566</v>
+        <v>5583399.2147067459</v>
       </c>
       <c r="U3">
         <v>7124382.24685532</v>
       </c>
       <c r="V3">
-        <v>133675.60270548405</v>
+        <v>475603.24148876639</v>
       </c>
       <c r="W3">
-        <v>71752.551197914072</v>
+        <v>7945.9749951001168</v>
       </c>
       <c r="X3">
-        <v>9847.616294423362</v>
+        <v>11099.075663762427</v>
       </c>
       <c r="Y3">
-        <v>1292.0447608169936</v>
+        <v>1216.4029719152352</v>
       </c>
       <c r="Z3">
-        <v>1393563.3822369259</v>
+        <v>1219367.9594573109</v>
       </c>
       <c r="AA3">
         <v>1274619.2944687847</v>
       </c>
       <c r="AB3">
-        <v>5128.0478724700852</v>
+        <v>18145.243129997052</v>
       </c>
       <c r="AC3">
-        <v>-0.20587147847627585</v>
+        <v>-0.022798487203060269</v>
       </c>
       <c r="AD3">
-        <v>0.21233415642723336</v>
+        <v>0.86018386176663741</v>
       </c>
       <c r="AE3">
-        <v>-9.2635784253528109E-06</v>
+        <v>-1.0258003219098082E-06</v>
       </c>
       <c r="AF3">
-        <v>9828.61202023126</v>
+        <v>10826.639924143785</v>
       </c>
       <c r="AG3">
-        <v>1292.0447607837082</v>
+        <v>1216.4029719148273</v>
       </c>
       <c r="AH3">
-        <v>1393582.3865111182</v>
+        <v>1219640.3951969293</v>
       </c>
       <c r="AI3">
-        <v>1274619.294468818</v>
+        <v>1274619.2944687852</v>
       </c>
       <c r="AJ3">
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>3.5972315286331083E-18</v>
       </c>
       <c r="AL3">
-        <v>1403410.9985313492</v>
+        <v>1230467.0351210733</v>
       </c>
       <c r="AM3">
-        <v>1275911.3392296017</v>
+        <v>1275835.6974407</v>
       </c>
       <c r="AN3">
-        <v>17895.395056927144</v>
+        <v>15635.500601707221</v>
       </c>
       <c r="AO3">
-        <v>13968.976164157424</v>
+        <v>13969.18586773903</v>
       </c>
       <c r="AP3">
         <v>50.042495777034276</v>
